--- a/artfynd/A 30678-2026 artfynd.xlsx
+++ b/artfynd/A 30678-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY171"/>
+  <dimension ref="A1:AZ171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70327986</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328058</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328101</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048225</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048243</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1274,6 +1304,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328037</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1371,6 +1406,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328051</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1478,6 +1518,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048161</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1585,6 +1630,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048177</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1692,6 +1742,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048183</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1799,6 +1854,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048202</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1906,6 +1966,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048203</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2013,6 +2078,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048350</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2120,6 +2190,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048366</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2217,6 +2292,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328090</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2324,6 +2404,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048348</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2421,6 +2506,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328100</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2528,6 +2618,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048179</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2635,6 +2730,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048195</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2742,6 +2842,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048236</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2849,6 +2954,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048251</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2956,6 +3066,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048269</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3063,6 +3178,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048385</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3160,6 +3280,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328056</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3267,6 +3392,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048356</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3364,6 +3494,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328050</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3471,6 +3606,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048234</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3568,6 +3708,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328018</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3665,6 +3810,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328043</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3762,6 +3912,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328076</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3859,6 +4014,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328083</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3966,6 +4126,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048372</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4073,6 +4238,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048157</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4170,6 +4340,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328095</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4267,6 +4442,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328098</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4364,6 +4544,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328107</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4471,6 +4656,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048155</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4578,6 +4768,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048171</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4685,6 +4880,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048173</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4792,6 +4992,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048176</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4899,6 +5104,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048178</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5006,6 +5216,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048180</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5113,6 +5328,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048186</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5220,6 +5440,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048191</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5327,6 +5552,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048199</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5434,6 +5664,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048204</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5541,6 +5776,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048205</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5648,6 +5888,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048206</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5755,6 +6000,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048211</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5862,6 +6112,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048212</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5969,6 +6224,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048221</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6076,6 +6336,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048227</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6183,6 +6448,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048239</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6290,6 +6560,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048271</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6397,6 +6672,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048276</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6504,6 +6784,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048278</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6611,6 +6896,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048282</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6718,6 +7008,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048289</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6825,6 +7120,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048295</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6932,6 +7232,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048302</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7039,6 +7344,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048316</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7146,6 +7456,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048335</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7253,6 +7568,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048344</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7360,6 +7680,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048364</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7467,6 +7792,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048370</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7574,6 +7904,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048187</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7671,6 +8006,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70327989</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7768,6 +8108,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328040</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7875,6 +8220,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048188</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7982,6 +8332,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048217</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8089,6 +8444,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048256</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8196,6 +8556,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048309</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8293,6 +8658,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70327978</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8390,6 +8760,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328089</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8497,6 +8872,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048346</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8604,6 +8984,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048368</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8701,6 +9086,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328032</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8798,6 +9188,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328045</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8895,6 +9290,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328081</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8992,6 +9392,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328116</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9099,6 +9504,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048190</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9206,6 +9616,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048229</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9303,6 +9718,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70327995</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9400,6 +9820,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328068</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9507,6 +9932,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048158</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9614,6 +10044,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048162</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9721,6 +10156,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048166</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9828,6 +10268,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048174</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9935,6 +10380,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048184</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10042,6 +10492,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048245</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10149,6 +10604,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048249</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10256,6 +10716,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048267</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10363,6 +10828,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048297</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10470,6 +10940,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048304</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10577,6 +11052,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048331</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10684,6 +11164,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048383</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10781,6 +11266,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328008</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10878,6 +11368,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328039</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10975,6 +11470,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328063</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11072,6 +11572,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328087</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11169,6 +11674,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328105</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11276,6 +11786,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048156</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11383,6 +11898,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048159</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11490,6 +12010,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048160</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11597,6 +12122,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048168</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11704,6 +12234,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048169</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11811,6 +12346,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048185</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11918,6 +12458,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048189</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12025,6 +12570,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048192</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12132,6 +12682,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048193</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12239,6 +12794,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048197</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12346,6 +12906,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048198</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12453,6 +13018,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048200</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12560,6 +13130,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048201</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12667,6 +13242,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048213</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12774,6 +13354,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048223</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12881,6 +13466,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048238</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12988,6 +13578,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048247</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13095,6 +13690,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048253</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13202,6 +13802,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048263</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13309,6 +13914,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048265</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13416,6 +14026,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048273</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13523,6 +14138,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048287</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13630,6 +14250,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048314</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13737,6 +14362,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048317</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13844,6 +14474,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048320</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13951,6 +14586,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048322</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14058,6 +14698,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048327</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14165,6 +14810,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048379</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14272,6 +14922,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048381</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14379,6 +15034,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048258</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14486,6 +15146,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048301</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14593,6 +15258,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048307</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14705,6 +15375,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048361</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14807,6 +15482,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328108</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14924,6 +15604,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048151</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -15041,6 +15726,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048181</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15158,6 +15848,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048182</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -15275,6 +15970,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048291</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15392,6 +16092,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048293</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15509,6 +16214,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048329</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15626,6 +16336,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048337</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15743,6 +16458,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048339</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -15860,6 +16580,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048341</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15977,6 +16702,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048352</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -16094,6 +16824,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048354</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -16205,6 +16940,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048210</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -16316,6 +17056,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048275</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -16427,6 +17172,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048324</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -16534,6 +17284,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048255</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -16641,6 +17396,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048311</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -16753,6 +17513,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048359</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -16850,6 +17615,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328049</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -16957,6 +17727,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048209</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -17064,6 +17839,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048215</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -17180,6 +17960,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048154</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -17277,6 +18062,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328102</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -17374,6 +18164,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328031</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -17471,6 +18266,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328064</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -17578,6 +18378,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048163</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -17685,6 +18490,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048208</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -17792,6 +18602,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048241</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -17899,6 +18714,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048262</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -18006,6 +18826,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048280</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -18113,6 +18938,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048285</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -18220,6 +19050,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048299</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -18327,6 +19162,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048306</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -18434,6 +19274,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048312</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -18541,6 +19386,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048333</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -18648,8 +19498,185 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135048170</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 30678-2026 artfynd.xlsx
+++ b/artfynd/A 30678-2026 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>135048225</v>
       </c>
       <c r="B5" t="n">
-        <v>97435</v>
+        <v>97479</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>135048243</v>
       </c>
       <c r="B6" t="n">
-        <v>97435</v>
+        <v>97479</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>135048161</v>
       </c>
       <c r="B9" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>135048177</v>
       </c>
       <c r="B10" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>135048183</v>
       </c>
       <c r="B11" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>135048202</v>
       </c>
       <c r="B12" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>135048203</v>
       </c>
       <c r="B13" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>135048350</v>
       </c>
       <c r="B14" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>135048366</v>
       </c>
       <c r="B15" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>135048348</v>
       </c>
       <c r="B17" t="n">
-        <v>83350</v>
+        <v>83390</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>135048179</v>
       </c>
       <c r="B19" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>135048195</v>
       </c>
       <c r="B20" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>135048236</v>
       </c>
       <c r="B21" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>135048251</v>
       </c>
       <c r="B22" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>135048269</v>
       </c>
       <c r="B23" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>135048385</v>
       </c>
       <c r="B24" t="n">
-        <v>79468</v>
+        <v>79506</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         <v>135048356</v>
       </c>
       <c r="B26" t="n">
-        <v>81355</v>
+        <v>81393</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>135048234</v>
       </c>
       <c r="B28" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>135048372</v>
       </c>
       <c r="B33" t="n">
-        <v>91995</v>
+        <v>92037</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4137,7 +4137,7 @@
         <v>135048157</v>
       </c>
       <c r="B34" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>135048155</v>
       </c>
       <c r="B38" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>135048171</v>
       </c>
       <c r="B39" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>135048173</v>
       </c>
       <c r="B40" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         <v>135048176</v>
       </c>
       <c r="B41" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         <v>135048178</v>
       </c>
       <c r="B42" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
         <v>135048180</v>
       </c>
       <c r="B43" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5227,7 +5227,7 @@
         <v>135048186</v>
       </c>
       <c r="B44" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>135048191</v>
       </c>
       <c r="B45" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5451,7 +5451,7 @@
         <v>135048199</v>
       </c>
       <c r="B46" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5563,7 +5563,7 @@
         <v>135048204</v>
       </c>
       <c r="B47" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         <v>135048205</v>
       </c>
       <c r="B48" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>135048206</v>
       </c>
       <c r="B49" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5899,7 +5899,7 @@
         <v>135048211</v>
       </c>
       <c r="B50" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6011,7 +6011,7 @@
         <v>135048212</v>
       </c>
       <c r="B51" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>135048221</v>
       </c>
       <c r="B52" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>135048227</v>
       </c>
       <c r="B53" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6347,7 +6347,7 @@
         <v>135048239</v>
       </c>
       <c r="B54" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>135048271</v>
       </c>
       <c r="B55" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6571,7 +6571,7 @@
         <v>135048276</v>
       </c>
       <c r="B56" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6683,7 +6683,7 @@
         <v>135048278</v>
       </c>
       <c r="B57" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6795,7 +6795,7 @@
         <v>135048282</v>
       </c>
       <c r="B58" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         <v>135048289</v>
       </c>
       <c r="B59" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>135048295</v>
       </c>
       <c r="B60" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         <v>135048302</v>
       </c>
       <c r="B61" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>135048316</v>
       </c>
       <c r="B62" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>135048335</v>
       </c>
       <c r="B63" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7467,7 +7467,7 @@
         <v>135048344</v>
       </c>
       <c r="B64" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>135048364</v>
       </c>
       <c r="B65" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7691,7 +7691,7 @@
         <v>135048370</v>
       </c>
       <c r="B66" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         <v>135048187</v>
       </c>
       <c r="B67" t="n">
-        <v>79397</v>
+        <v>79435</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>135048188</v>
       </c>
       <c r="B70" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>135048217</v>
       </c>
       <c r="B71" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8343,7 +8343,7 @@
         <v>135048256</v>
       </c>
       <c r="B72" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8455,7 +8455,7 @@
         <v>135048309</v>
       </c>
       <c r="B73" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         <v>135048346</v>
       </c>
       <c r="B76" t="n">
-        <v>83341</v>
+        <v>83381</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8883,7 +8883,7 @@
         <v>135048368</v>
       </c>
       <c r="B77" t="n">
-        <v>83341</v>
+        <v>83381</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
         <v>135048190</v>
       </c>
       <c r="B82" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>135048229</v>
       </c>
       <c r="B83" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9831,7 +9831,7 @@
         <v>135048158</v>
       </c>
       <c r="B86" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9943,7 +9943,7 @@
         <v>135048162</v>
       </c>
       <c r="B87" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10055,7 +10055,7 @@
         <v>135048166</v>
       </c>
       <c r="B88" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10167,7 +10167,7 @@
         <v>135048174</v>
       </c>
       <c r="B89" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10279,7 +10279,7 @@
         <v>135048184</v>
       </c>
       <c r="B90" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
         <v>135048245</v>
       </c>
       <c r="B91" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10503,7 +10503,7 @@
         <v>135048249</v>
       </c>
       <c r="B92" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10615,7 +10615,7 @@
         <v>135048267</v>
       </c>
       <c r="B93" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10727,7 +10727,7 @@
         <v>135048297</v>
       </c>
       <c r="B94" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10839,7 +10839,7 @@
         <v>135048304</v>
       </c>
       <c r="B95" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>135048331</v>
       </c>
       <c r="B96" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11063,7 +11063,7 @@
         <v>135048383</v>
       </c>
       <c r="B97" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11685,7 +11685,7 @@
         <v>135048156</v>
       </c>
       <c r="B103" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11797,7 +11797,7 @@
         <v>135048159</v>
       </c>
       <c r="B104" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11909,7 +11909,7 @@
         <v>135048160</v>
       </c>
       <c r="B105" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12021,7 +12021,7 @@
         <v>135048168</v>
       </c>
       <c r="B106" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12133,7 +12133,7 @@
         <v>135048169</v>
       </c>
       <c r="B107" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12245,7 +12245,7 @@
         <v>135048185</v>
       </c>
       <c r="B108" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12357,7 +12357,7 @@
         <v>135048189</v>
       </c>
       <c r="B109" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12469,7 +12469,7 @@
         <v>135048192</v>
       </c>
       <c r="B110" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
         <v>135048193</v>
       </c>
       <c r="B111" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12693,7 +12693,7 @@
         <v>135048197</v>
       </c>
       <c r="B112" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12805,7 +12805,7 @@
         <v>135048198</v>
       </c>
       <c r="B113" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12917,7 +12917,7 @@
         <v>135048200</v>
       </c>
       <c r="B114" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>135048201</v>
       </c>
       <c r="B115" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13141,7 +13141,7 @@
         <v>135048213</v>
       </c>
       <c r="B116" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13253,7 +13253,7 @@
         <v>135048223</v>
       </c>
       <c r="B117" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13365,7 +13365,7 @@
         <v>135048238</v>
       </c>
       <c r="B118" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13477,7 +13477,7 @@
         <v>135048247</v>
       </c>
       <c r="B119" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13589,7 +13589,7 @@
         <v>135048253</v>
       </c>
       <c r="B120" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13701,7 +13701,7 @@
         <v>135048263</v>
       </c>
       <c r="B121" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13813,7 +13813,7 @@
         <v>135048265</v>
       </c>
       <c r="B122" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13925,7 +13925,7 @@
         <v>135048273</v>
       </c>
       <c r="B123" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14037,7 +14037,7 @@
         <v>135048287</v>
       </c>
       <c r="B124" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14149,7 +14149,7 @@
         <v>135048314</v>
       </c>
       <c r="B125" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14261,7 +14261,7 @@
         <v>135048317</v>
       </c>
       <c r="B126" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14373,7 +14373,7 @@
         <v>135048320</v>
       </c>
       <c r="B127" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14485,7 +14485,7 @@
         <v>135048322</v>
       </c>
       <c r="B128" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14597,7 +14597,7 @@
         <v>135048327</v>
       </c>
       <c r="B129" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14709,7 +14709,7 @@
         <v>135048379</v>
       </c>
       <c r="B130" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14821,7 +14821,7 @@
         <v>135048381</v>
       </c>
       <c r="B131" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14933,7 +14933,7 @@
         <v>135048258</v>
       </c>
       <c r="B132" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15045,7 +15045,7 @@
         <v>135048301</v>
       </c>
       <c r="B133" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15157,7 +15157,7 @@
         <v>135048307</v>
       </c>
       <c r="B134" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15269,7 +15269,7 @@
         <v>135048361</v>
       </c>
       <c r="B135" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15493,7 +15493,7 @@
         <v>135048151</v>
       </c>
       <c r="B137" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15615,7 +15615,7 @@
         <v>135048181</v>
       </c>
       <c r="B138" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15737,7 +15737,7 @@
         <v>135048182</v>
       </c>
       <c r="B139" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15859,7 +15859,7 @@
         <v>135048291</v>
       </c>
       <c r="B140" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15981,7 +15981,7 @@
         <v>135048293</v>
       </c>
       <c r="B141" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16103,7 +16103,7 @@
         <v>135048329</v>
       </c>
       <c r="B142" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16225,7 +16225,7 @@
         <v>135048337</v>
       </c>
       <c r="B143" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16347,7 +16347,7 @@
         <v>135048339</v>
       </c>
       <c r="B144" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16469,7 +16469,7 @@
         <v>135048341</v>
       </c>
       <c r="B145" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16591,7 +16591,7 @@
         <v>135048352</v>
       </c>
       <c r="B146" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16713,7 +16713,7 @@
         <v>135048354</v>
       </c>
       <c r="B147" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16835,7 +16835,7 @@
         <v>135048210</v>
       </c>
       <c r="B148" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16951,7 +16951,7 @@
         <v>135048275</v>
       </c>
       <c r="B149" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17067,7 +17067,7 @@
         <v>135048324</v>
       </c>
       <c r="B150" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17183,7 +17183,7 @@
         <v>135048255</v>
       </c>
       <c r="B151" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17295,7 +17295,7 @@
         <v>135048311</v>
       </c>
       <c r="B152" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17407,7 +17407,7 @@
         <v>135048359</v>
       </c>
       <c r="B153" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17626,7 +17626,7 @@
         <v>135048209</v>
       </c>
       <c r="B155" t="n">
-        <v>108205</v>
+        <v>108260</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17738,7 +17738,7 @@
         <v>135048215</v>
       </c>
       <c r="B156" t="n">
-        <v>108205</v>
+        <v>108260</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17850,7 +17850,7 @@
         <v>135048154</v>
       </c>
       <c r="B157" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18277,7 +18277,7 @@
         <v>135048163</v>
       </c>
       <c r="B161" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18389,7 +18389,7 @@
         <v>135048208</v>
       </c>
       <c r="B162" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18501,7 +18501,7 @@
         <v>135048241</v>
       </c>
       <c r="B163" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18613,7 +18613,7 @@
         <v>135048262</v>
       </c>
       <c r="B164" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18725,7 +18725,7 @@
         <v>135048280</v>
       </c>
       <c r="B165" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18837,7 +18837,7 @@
         <v>135048285</v>
       </c>
       <c r="B166" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18949,7 +18949,7 @@
         <v>135048299</v>
       </c>
       <c r="B167" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19061,7 +19061,7 @@
         <v>135048306</v>
       </c>
       <c r="B168" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19173,7 +19173,7 @@
         <v>135048312</v>
       </c>
       <c r="B169" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19285,7 +19285,7 @@
         <v>135048333</v>
       </c>
       <c r="B170" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19397,7 +19397,7 @@
         <v>135048170</v>
       </c>
       <c r="B171" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>

--- a/artfynd/A 30678-2026 artfynd.xlsx
+++ b/artfynd/A 30678-2026 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>135048225</v>
       </c>
       <c r="B5" t="n">
-        <v>97479</v>
+        <v>97506</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>135048243</v>
       </c>
       <c r="B6" t="n">
-        <v>97479</v>
+        <v>97506</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>135048161</v>
       </c>
       <c r="B9" t="n">
-        <v>79443</v>
+        <v>79470</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>135048177</v>
       </c>
       <c r="B10" t="n">
-        <v>79443</v>
+        <v>79470</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>135048183</v>
       </c>
       <c r="B11" t="n">
-        <v>79443</v>
+        <v>79470</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>135048202</v>
       </c>
       <c r="B12" t="n">
-        <v>79443</v>
+        <v>79470</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>135048203</v>
       </c>
       <c r="B13" t="n">
-        <v>79443</v>
+        <v>79470</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>135048350</v>
       </c>
       <c r="B14" t="n">
-        <v>79443</v>
+        <v>79470</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>135048366</v>
       </c>
       <c r="B15" t="n">
-        <v>79443</v>
+        <v>79470</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>135048348</v>
       </c>
       <c r="B17" t="n">
-        <v>83390</v>
+        <v>83417</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>135048179</v>
       </c>
       <c r="B19" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>135048195</v>
       </c>
       <c r="B20" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>135048236</v>
       </c>
       <c r="B21" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>135048251</v>
       </c>
       <c r="B22" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>135048269</v>
       </c>
       <c r="B23" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>135048385</v>
       </c>
       <c r="B24" t="n">
-        <v>79506</v>
+        <v>79533</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         <v>135048356</v>
       </c>
       <c r="B26" t="n">
-        <v>81393</v>
+        <v>81420</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>135048234</v>
       </c>
       <c r="B28" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>135048372</v>
       </c>
       <c r="B33" t="n">
-        <v>92037</v>
+        <v>92064</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4137,7 +4137,7 @@
         <v>135048157</v>
       </c>
       <c r="B34" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>135048155</v>
       </c>
       <c r="B38" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>135048171</v>
       </c>
       <c r="B39" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>135048173</v>
       </c>
       <c r="B40" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         <v>135048176</v>
       </c>
       <c r="B41" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         <v>135048178</v>
       </c>
       <c r="B42" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
         <v>135048180</v>
       </c>
       <c r="B43" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5227,7 +5227,7 @@
         <v>135048186</v>
       </c>
       <c r="B44" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>135048191</v>
       </c>
       <c r="B45" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5451,7 +5451,7 @@
         <v>135048199</v>
       </c>
       <c r="B46" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5563,7 +5563,7 @@
         <v>135048204</v>
       </c>
       <c r="B47" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         <v>135048205</v>
       </c>
       <c r="B48" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>135048206</v>
       </c>
       <c r="B49" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5899,7 +5899,7 @@
         <v>135048211</v>
       </c>
       <c r="B50" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6011,7 +6011,7 @@
         <v>135048212</v>
       </c>
       <c r="B51" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>135048221</v>
       </c>
       <c r="B52" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>135048227</v>
       </c>
       <c r="B53" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6347,7 +6347,7 @@
         <v>135048239</v>
       </c>
       <c r="B54" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>135048271</v>
       </c>
       <c r="B55" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6571,7 +6571,7 @@
         <v>135048276</v>
       </c>
       <c r="B56" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6683,7 +6683,7 @@
         <v>135048278</v>
       </c>
       <c r="B57" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6795,7 +6795,7 @@
         <v>135048282</v>
       </c>
       <c r="B58" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         <v>135048289</v>
       </c>
       <c r="B59" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>135048295</v>
       </c>
       <c r="B60" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         <v>135048302</v>
       </c>
       <c r="B61" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>135048316</v>
       </c>
       <c r="B62" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>135048335</v>
       </c>
       <c r="B63" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7467,7 +7467,7 @@
         <v>135048344</v>
       </c>
       <c r="B64" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>135048364</v>
       </c>
       <c r="B65" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7691,7 +7691,7 @@
         <v>135048370</v>
       </c>
       <c r="B66" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         <v>135048187</v>
       </c>
       <c r="B67" t="n">
-        <v>79435</v>
+        <v>79462</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>135048188</v>
       </c>
       <c r="B70" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>135048217</v>
       </c>
       <c r="B71" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8343,7 +8343,7 @@
         <v>135048256</v>
       </c>
       <c r="B72" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8455,7 +8455,7 @@
         <v>135048309</v>
       </c>
       <c r="B73" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         <v>135048346</v>
       </c>
       <c r="B76" t="n">
-        <v>83381</v>
+        <v>83408</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8883,7 +8883,7 @@
         <v>135048368</v>
       </c>
       <c r="B77" t="n">
-        <v>83381</v>
+        <v>83408</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
         <v>135048190</v>
       </c>
       <c r="B82" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>135048229</v>
       </c>
       <c r="B83" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9831,7 +9831,7 @@
         <v>135048158</v>
       </c>
       <c r="B86" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9943,7 +9943,7 @@
         <v>135048162</v>
       </c>
       <c r="B87" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10055,7 +10055,7 @@
         <v>135048166</v>
       </c>
       <c r="B88" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10167,7 +10167,7 @@
         <v>135048174</v>
       </c>
       <c r="B89" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10279,7 +10279,7 @@
         <v>135048184</v>
       </c>
       <c r="B90" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
         <v>135048245</v>
       </c>
       <c r="B91" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10503,7 +10503,7 @@
         <v>135048249</v>
       </c>
       <c r="B92" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10615,7 +10615,7 @@
         <v>135048267</v>
       </c>
       <c r="B93" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10727,7 +10727,7 @@
         <v>135048297</v>
       </c>
       <c r="B94" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10839,7 +10839,7 @@
         <v>135048304</v>
       </c>
       <c r="B95" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>135048331</v>
       </c>
       <c r="B96" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11063,7 +11063,7 @@
         <v>135048383</v>
       </c>
       <c r="B97" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11685,7 +11685,7 @@
         <v>135048156</v>
       </c>
       <c r="B103" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11797,7 +11797,7 @@
         <v>135048159</v>
       </c>
       <c r="B104" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11909,7 +11909,7 @@
         <v>135048160</v>
       </c>
       <c r="B105" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12021,7 +12021,7 @@
         <v>135048168</v>
       </c>
       <c r="B106" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12133,7 +12133,7 @@
         <v>135048169</v>
       </c>
       <c r="B107" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12245,7 +12245,7 @@
         <v>135048185</v>
       </c>
       <c r="B108" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12357,7 +12357,7 @@
         <v>135048189</v>
       </c>
       <c r="B109" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12469,7 +12469,7 @@
         <v>135048192</v>
       </c>
       <c r="B110" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
         <v>135048193</v>
       </c>
       <c r="B111" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12693,7 +12693,7 @@
         <v>135048197</v>
       </c>
       <c r="B112" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12805,7 +12805,7 @@
         <v>135048198</v>
       </c>
       <c r="B113" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12917,7 +12917,7 @@
         <v>135048200</v>
       </c>
       <c r="B114" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>135048201</v>
       </c>
       <c r="B115" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13141,7 +13141,7 @@
         <v>135048213</v>
       </c>
       <c r="B116" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13253,7 +13253,7 @@
         <v>135048223</v>
       </c>
       <c r="B117" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13365,7 +13365,7 @@
         <v>135048238</v>
       </c>
       <c r="B118" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13477,7 +13477,7 @@
         <v>135048247</v>
       </c>
       <c r="B119" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13589,7 +13589,7 @@
         <v>135048253</v>
       </c>
       <c r="B120" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13701,7 +13701,7 @@
         <v>135048263</v>
       </c>
       <c r="B121" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13813,7 +13813,7 @@
         <v>135048265</v>
       </c>
       <c r="B122" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13925,7 +13925,7 @@
         <v>135048273</v>
       </c>
       <c r="B123" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14037,7 +14037,7 @@
         <v>135048287</v>
       </c>
       <c r="B124" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14149,7 +14149,7 @@
         <v>135048314</v>
       </c>
       <c r="B125" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14261,7 +14261,7 @@
         <v>135048317</v>
       </c>
       <c r="B126" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14373,7 +14373,7 @@
         <v>135048320</v>
       </c>
       <c r="B127" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14485,7 +14485,7 @@
         <v>135048322</v>
       </c>
       <c r="B128" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14597,7 +14597,7 @@
         <v>135048327</v>
       </c>
       <c r="B129" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14709,7 +14709,7 @@
         <v>135048379</v>
       </c>
       <c r="B130" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14821,7 +14821,7 @@
         <v>135048381</v>
       </c>
       <c r="B131" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14933,7 +14933,7 @@
         <v>135048258</v>
       </c>
       <c r="B132" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15045,7 +15045,7 @@
         <v>135048301</v>
       </c>
       <c r="B133" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15157,7 +15157,7 @@
         <v>135048307</v>
       </c>
       <c r="B134" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -17626,7 +17626,7 @@
         <v>135048209</v>
       </c>
       <c r="B155" t="n">
-        <v>108260</v>
+        <v>108287</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17738,7 +17738,7 @@
         <v>135048215</v>
       </c>
       <c r="B156" t="n">
-        <v>108260</v>
+        <v>108287</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17850,7 +17850,7 @@
         <v>135048154</v>
       </c>
       <c r="B157" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18277,7 +18277,7 @@
         <v>135048163</v>
       </c>
       <c r="B161" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18389,7 +18389,7 @@
         <v>135048208</v>
       </c>
       <c r="B162" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18501,7 +18501,7 @@
         <v>135048241</v>
       </c>
       <c r="B163" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18613,7 +18613,7 @@
         <v>135048262</v>
       </c>
       <c r="B164" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18725,7 +18725,7 @@
         <v>135048280</v>
       </c>
       <c r="B165" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18837,7 +18837,7 @@
         <v>135048285</v>
       </c>
       <c r="B166" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18949,7 +18949,7 @@
         <v>135048299</v>
       </c>
       <c r="B167" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19061,7 +19061,7 @@
         <v>135048306</v>
       </c>
       <c r="B168" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19173,7 +19173,7 @@
         <v>135048312</v>
       </c>
       <c r="B169" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19285,7 +19285,7 @@
         <v>135048333</v>
       </c>
       <c r="B170" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19397,7 +19397,7 @@
         <v>135048170</v>
       </c>
       <c r="B171" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
